--- a/tests/FatEq_C_x_13M_SemMotobox_D4_0004.xlsx
+++ b/tests/FatEq_C_x_13M_SemMotobox_D4_0004.xlsx
@@ -533,21 +533,21 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>15.07</v>
+        <v>32.73</v>
       </c>
       <c r="F2" t="n">
-        <v>19.07</v>
+        <v>36.73</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[8,4,13,2]</t>
+          <t>[8,4,13,2,6,7,45,50,58,61,65]</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -575,11 +575,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[11,22,17,20,19,14,15,12]</t>
+          <t>[11,22,17,20,19,14,15,23,12,18,25,24,21,38,43]</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -600,21 +600,21 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>22.33</v>
+        <v>41.07</v>
       </c>
       <c r="F3" t="n">
-        <v>26.33</v>
+        <v>45.07</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[10,9,1,3,5,26,41]</t>
+          <t>[10,9,1,3,5,26,41,47,57,60,71,74,79,83,86]</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -642,11 +642,11 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[11,22,17,20,19,14,15,23,12,18,16,25,24,21,38,43]</t>
+          <t>[11,17,19,15,23,18,16,25,24,21,38,67,64,72]</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -667,21 +667,21 @@
         <v>164</v>
       </c>
       <c r="E4" t="n">
-        <v>25.09999999999999</v>
+        <v>32.33000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>189.1</v>
+        <v>196.33</v>
       </c>
       <c r="G4" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[166,167,169,203,208,213]</t>
+          <t>[166,167,169,203,208,213,224,233,240]</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -709,11 +709,11 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[162,163,174,164,176,186,179,182,184,187]</t>
+          <t>[162,163,174,164,176,178,186,179,182,185,184,187,191,192,210,228]</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -734,21 +734,21 @@
         <v>164</v>
       </c>
       <c r="E5" t="n">
-        <v>43.53</v>
+        <v>50.03</v>
       </c>
       <c r="F5" t="n">
-        <v>207.53</v>
+        <v>214.03</v>
       </c>
       <c r="G5" t="n">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[156,159,161,165,201,206,212,221,232,241,247,251,257,260,268]</t>
+          <t>[156,159,161,165,201,206,212,221,232,241,247,251,257,260,268,274,283]</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -776,11 +776,11 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[162,163,174,164,177,176,178,179,182,185,184,187,191,192,210,228]</t>
+          <t>[164,177,178,185,191,192,210,228]</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -794,28 +794,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Headway entre veículos foi elevado</t>
+          <t>Fluxo interrompido por algum evento</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>324</v>
       </c>
       <c r="E6" t="n">
-        <v>28.30000000000001</v>
+        <v>41.47000000000003</v>
       </c>
       <c r="F6" t="n">
-        <v>352.3</v>
+        <v>365.47</v>
       </c>
       <c r="G6" t="n">
-        <v>406</v>
+        <v>437</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[306,307,309,346,347,374,399,406]</t>
+          <t>[306,307,309,346,347,374,399,406,413,418,420,430,437]</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[320,313,312,327,344,314,355,318,336,339,353,325,356,333,385,389]</t>
+          <t>[320,313,312,327,344,314,317,355,318,319,324,326,336,339,343,353,325,356,333,385,395,389,415,426]</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -861,28 +861,28 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Headway entre veículos foi elevado</t>
+          <t>Fluxo interrompido por algum evento</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>324</v>
       </c>
       <c r="E7" t="n">
-        <v>22.39999999999998</v>
+        <v>40.30000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>346.4</v>
+        <v>364.3</v>
       </c>
       <c r="G7" t="n">
-        <v>381</v>
+        <v>442</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[308,311,337,340,363,375,381]</t>
+          <t>[308,311,337,340,363,375,381,401,411,414,428,442]</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -894,27 +894,27 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[423]</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[391]</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[320,310,312,315,316,327,344,317,355,318,319,322,324,326,336,339,323,343,353,356,385]</t>
+          <t>[310,315,316,317,318,319,322,324,326,336,339,323,343,353,356,385,395,424,425,426]</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -977,11 +977,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[505,509,522,519,525,547,551,555,539,548,549,559,550,608,606,603,614]</t>
+          <t>[505,509,522,519,525,547,551,532,533,555,539,546,548,549,559,550,601,608,606,603,614,618]</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1002,21 +1002,21 @@
         <v>484</v>
       </c>
       <c r="E9" t="n">
-        <v>13.23000000000002</v>
+        <v>41.37</v>
       </c>
       <c r="F9" t="n">
-        <v>497.23</v>
+        <v>525.37</v>
       </c>
       <c r="G9" t="n">
-        <v>536</v>
+        <v>645</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[499,529,535,536]</t>
+          <t>[499,529,535,536,538,585,592,600,609,617,624,629,636,641,645]</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1044,11 +1044,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[505,522,526,511,525,515,547,551,532,527,533,555,539,542,546,548,549]</t>
+          <t>[505,526,511,525,515,532,527,533,539,542,546,548,549,559,541,601,608,618,628]</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
